--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -21693,16 +21693,16 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O128" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q128" t="n">
         <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>0.5545945847474882</v>
+        <v>0.5509217729279685</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -24361,16 +24361,16 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O144" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Q144" t="n">
         <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>0.08080186002943539</v>
+        <v>0.08814748366847497</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>347716</v>
+        <v>347717</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -23181,16 +23181,16 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O134" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q134" t="n">
         <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>0.5509217729279685</v>
+        <v>0.5545945847474882</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -25849,16 +25849,16 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="O150" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="Q150" t="n">
         <v>0</v>
       </c>
       <c r="R150" t="n">
-        <v>0.09549310730751455</v>
+        <v>0.1322212255027125</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -26867,6 +26867,154 @@
       <c r="BC155" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N156" t="n">
+        <v>272</v>
+      </c>
+      <c r="O156" t="n">
+        <v>272</v>
+      </c>
+      <c r="Q156" t="n">
+        <v>0</v>
+      </c>
+      <c r="R156" t="n">
+        <v>0.2221718868578884</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO156" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP156" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr"/>
+      <c r="AT156" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU156" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV156" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA156" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB156" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC156" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26903,7 +27051,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -26986,7 +27134,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10">
@@ -26996,7 +27144,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11">
@@ -27048,7 +27196,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>347722</v>
+        <v>348005</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>55</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>46</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.5106686451006117</v>
       </c>
@@ -1602,9 +1596,6 @@
       <c r="O7" t="n">
         <v>15</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.2668213756296206</v>
       </c>
@@ -1998,9 +1989,6 @@
       <c r="O9" t="n">
         <v>271</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>3.672782459333082</v>
       </c>
@@ -2146,9 +2134,6 @@
       <c r="O10" t="n">
         <v>8</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.1415180660636405</v>
       </c>
@@ -2791,7 +2776,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -2938,9 +2923,6 @@
       <c r="O14" t="n">
         <v>24</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.2242771302788003</v>
       </c>
@@ -4814,9 +4796,6 @@
       <c r="O26" t="n">
         <v>58</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5207,9 +5186,6 @@
       <c r="O28" t="n">
         <v>44</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.4884656605310199</v>
       </c>
@@ -5503,9 +5479,6 @@
       <c r="O30" t="n">
         <v>15</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.2668213756296206</v>
       </c>
@@ -5899,9 +5872,6 @@
       <c r="O32" t="n">
         <v>194</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>2.629224343581616</v>
       </c>
@@ -6047,9 +6017,6 @@
       <c r="O33" t="n">
         <v>12</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.2122770990954608</v>
       </c>
@@ -6692,7 +6659,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN36" t="b">
@@ -6839,9 +6806,6 @@
       <c r="O37" t="n">
         <v>23</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.214932249850517</v>
       </c>
@@ -8567,9 +8531,6 @@
       <c r="O48" t="n">
         <v>64</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8960,9 +8921,6 @@
       <c r="O50" t="n">
         <v>42</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.4662626759614281</v>
       </c>
@@ -9256,9 +9214,6 @@
       <c r="O52" t="n">
         <v>20</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.3557618341728275</v>
       </c>
@@ -9652,9 +9607,6 @@
       <c r="O54" t="n">
         <v>224</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>3.035805427640629</v>
       </c>
@@ -9800,9 +9752,6 @@
       <c r="O55" t="n">
         <v>15</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.2653463738693259</v>
       </c>
@@ -10445,7 +10394,7 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN58" t="b">
@@ -10592,9 +10541,6 @@
       <c r="O59" t="n">
         <v>26</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.242966891135367</v>
       </c>
@@ -12172,9 +12118,6 @@
       <c r="O69" t="n">
         <v>119</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.4370646065228551</v>
       </c>
@@ -12320,9 +12263,6 @@
       <c r="O70" t="n">
         <v>56</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="S70" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12713,9 +12653,6 @@
       <c r="O72" t="n">
         <v>28</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.3108417839742854</v>
       </c>
@@ -13009,9 +12946,6 @@
       <c r="O74" t="n">
         <v>9</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.1600928253777724</v>
       </c>
@@ -13405,9 +13339,6 @@
       <c r="O76" t="n">
         <v>222</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>3.008700022036694</v>
       </c>
@@ -13553,9 +13484,6 @@
       <c r="O77" t="n">
         <v>9</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.1592078243215956</v>
       </c>
@@ -13949,9 +13877,6 @@
       <c r="O79" t="n">
         <v>35</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.6619411632651402</v>
       </c>
@@ -14198,7 +14123,7 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN80" t="b">
@@ -14345,9 +14270,6 @@
       <c r="O81" t="n">
         <v>25</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.2336220107070837</v>
       </c>
@@ -15925,9 +15847,6 @@
       <c r="O91" t="n">
         <v>112</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.4113549237862165</v>
       </c>
@@ -16073,9 +15992,6 @@
       <c r="O92" t="n">
         <v>69</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16466,9 +16382,6 @@
       <c r="O94" t="n">
         <v>49</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.5439731219549995</v>
       </c>
@@ -16762,9 +16675,6 @@
       <c r="O96" t="n">
         <v>15</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.2668213756296206</v>
       </c>
@@ -17158,9 +17068,6 @@
       <c r="O98" t="n">
         <v>251</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>3.40172840329374</v>
       </c>
@@ -17306,9 +17213,6 @@
       <c r="O99" t="n">
         <v>12</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.2122770990954608</v>
       </c>
@@ -17702,9 +17606,6 @@
       <c r="O101" t="n">
         <v>32</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.6052033492709853</v>
       </c>
@@ -17951,7 +17852,7 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -18098,9 +17999,6 @@
       <c r="O103" t="n">
         <v>22</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.2055873694222336</v>
       </c>
@@ -19826,9 +19724,6 @@
       <c r="O114" t="n">
         <v>68</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.01948225930283182</v>
       </c>
@@ -19974,9 +19869,6 @@
       <c r="O115" t="n">
         <v>117</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.4297189828838154</v>
       </c>
@@ -20270,9 +20162,6 @@
       <c r="O117" t="n">
         <v>15</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.2668213756296206</v>
       </c>
@@ -20666,9 +20555,6 @@
       <c r="O119" t="n">
         <v>262</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>3.550808134115378</v>
       </c>
@@ -20814,9 +20700,6 @@
       <c r="O120" t="n">
         <v>20</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.3537951651591013</v>
       </c>
@@ -21210,9 +21093,6 @@
       <c r="O122" t="n">
         <v>43</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.8132420005828864</v>
       </c>
@@ -21459,7 +21339,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -21606,9 +21486,6 @@
       <c r="O124" t="n">
         <v>25</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.2336220107070837</v>
       </c>
@@ -22002,9 +21879,6 @@
       <c r="O126" t="n">
         <v>273</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.2229886952654542</v>
       </c>
@@ -22150,9 +22024,6 @@
       <c r="O127" t="n">
         <v>84</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.02406632031526284</v>
       </c>
@@ -22298,9 +22169,6 @@
       <c r="O128" t="n">
         <v>271</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.2213550784503227</v>
       </c>
@@ -22446,9 +22314,6 @@
       <c r="O129" t="n">
         <v>68</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.01948225930283182</v>
       </c>
@@ -22594,9 +22459,6 @@
       <c r="O130" t="n">
         <v>229</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.1870491253325605</v>
       </c>
@@ -22742,9 +22604,6 @@
       <c r="O131" t="n">
         <v>51</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.01461169447712387</v>
       </c>
@@ -22890,9 +22749,6 @@
       <c r="O132" t="n">
         <v>265</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.2164542280049281</v>
       </c>
@@ -23038,9 +22894,6 @@
       <c r="O133" t="n">
         <v>93</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.02664485463475528</v>
       </c>
@@ -23186,9 +23039,6 @@
       <c r="O134" t="n">
         <v>151</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.5545945847474882</v>
       </c>
@@ -23334,9 +23184,6 @@
       <c r="O135" t="n">
         <v>12</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.2134571005036965</v>
       </c>
@@ -23725,16 +23572,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O137" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R137" t="n">
-        <v>0.07075903303182025</v>
+        <v>0.08844879128977531</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -23887,10 +23731,10 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O138" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U138" t="inlineStr">
         <is>
@@ -24126,9 +23970,6 @@
       <c r="O139" t="n">
         <v>26</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.242966891135367</v>
       </c>
@@ -24522,9 +24363,6 @@
       <c r="O141" t="n">
         <v>213</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.1739801908115082</v>
       </c>
@@ -24670,9 +24508,6 @@
       <c r="O142" t="n">
         <v>62</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.01776323642317019</v>
       </c>
@@ -24818,9 +24653,6 @@
       <c r="O143" t="n">
         <v>232</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.1894995505552578</v>
       </c>
@@ -24966,9 +24798,6 @@
       <c r="O144" t="n">
         <v>113</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.03237493090029405</v>
       </c>
@@ -25114,9 +24943,6 @@
       <c r="O145" t="n">
         <v>247</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.2017516766687443</v>
       </c>
@@ -25262,9 +25088,6 @@
       <c r="O146" t="n">
         <v>64</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.01833624404972407</v>
       </c>
@@ -25410,9 +25233,6 @@
       <c r="O147" t="n">
         <v>244</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.199301251446047</v>
       </c>
@@ -25558,9 +25378,6 @@
       <c r="O148" t="n">
         <v>75</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.02148778599577039</v>
       </c>
@@ -25706,9 +25523,6 @@
       <c r="O149" t="n">
         <v>225</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.1837818917022974</v>
       </c>
@@ -25854,9 +25668,6 @@
       <c r="O150" t="n">
         <v>36</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.1322212255027125</v>
       </c>
@@ -26002,9 +25813,6 @@
       <c r="O151" t="n">
         <v>3</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.05336427512592412</v>
       </c>
@@ -26398,9 +26206,6 @@
       <c r="O153" t="n">
         <v>1</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -26794,9 +26599,6 @@
       <c r="O155" t="n">
         <v>72</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.02062827455593957</v>
       </c>
@@ -26942,9 +26744,6 @@
       <c r="O156" t="n">
         <v>272</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.2221718868578884</v>
       </c>
@@ -27015,6 +26814,151 @@
       <c r="BC156" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N157" t="n">
+        <v>103</v>
+      </c>
+      <c r="O157" t="n">
+        <v>103</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0.02950989276752467</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO157" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP157" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
+      <c r="AT157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU157" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV157" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW157" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX157" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY157" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA157" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB157" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC157" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27051,7 +26995,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -27134,7 +27078,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10">
@@ -27144,7 +27088,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -27196,7 +27140,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>348005</v>
+        <v>348109</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -23034,13 +23034,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O134" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R134" t="n">
-        <v>0.5545945847474882</v>
+        <v>0.5582673965670081</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23179,13 +23179,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O135" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R135" t="n">
-        <v>0.2134571005036965</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23338,10 +23338,10 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O136" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U136" t="inlineStr">
         <is>
@@ -25663,13 +25663,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="O150" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="R150" t="n">
-        <v>0.1322212255027125</v>
+        <v>0.1836405909759895</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>348109</v>
+        <v>348123</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O3" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -8526,10 +8526,10 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O48" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
@@ -8682,10 +8682,10 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O49" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U49" t="inlineStr">
         <is>
@@ -12258,10 +12258,10 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O70" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -12414,10 +12414,10 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O71" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="U71" t="inlineStr">
         <is>
@@ -15987,10 +15987,10 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O92" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -16143,10 +16143,10 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O93" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="U93" t="inlineStr">
         <is>
@@ -19970,12 +19970,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -20009,84 +20009,92 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>56491</v>
+        <v>72</v>
       </c>
       <c r="O116" t="n">
-        <v>56491</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>183</v>
-      </c>
-      <c r="R116" t="n">
-        <v>3.998190722266268</v>
+        <v>72</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ACTIVE_TUBERCULOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS116" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ116" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ACTIVE_TUBERCULOSIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20113,17 +20121,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -20157,22 +20165,39 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>15</v>
+        <v>72</v>
       </c>
       <c r="O117" t="n">
-        <v>15</v>
-      </c>
-      <c r="R117" t="n">
-        <v>0.2668213756296206</v>
-      </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>72</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_700</t>
+          <t>SER_CA_ON_PHO_IDTO_ACTIVE_TUBERCULOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_ACTIVE_TUBERCULOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -20180,6 +20205,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD117" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE117" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG117" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary active tuberculosis notifications; confirmed cases only, excluding latent tuberculosis infection, and classified by Diagnosis Date.</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN117" t="b">
+        <v>1</v>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -20192,12 +20275,12 @@
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_700</t>
+          <t>SER_CA_ON_PHO_IDTO_ACTIVE_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT117" t="n">
@@ -20205,47 +20288,47 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -20272,17 +20355,17 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -20316,170 +20399,84 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>15</v>
+        <v>56491</v>
       </c>
       <c r="O118" t="n">
-        <v>15</v>
-      </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="V118" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>Tuberculosis, total</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD118" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE118" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF118" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG118" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM118" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN118" t="b">
-        <v>1</v>
+        <v>56491</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>183</v>
+      </c>
+      <c r="R118" t="n">
+        <v>3.998190722266268</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -20511,12 +20508,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -20550,81 +20547,95 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>262</v>
+        <v>15</v>
       </c>
       <c r="O119" t="n">
-        <v>262</v>
+        <v>15</v>
       </c>
       <c r="R119" t="n">
-        <v>3.550808134115378</v>
+        <v>0.2668213756296206</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ119" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
       <c r="AT119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20651,17 +20662,17 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -20695,22 +20706,39 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="O120" t="n">
-        <v>20</v>
-      </c>
-      <c r="R120" t="n">
-        <v>0.3537951651591013</v>
-      </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>15</v>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>Tuberculosis, total</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -20718,6 +20746,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE120" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG120" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM120" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN120" t="b">
+        <v>1</v>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -20730,12 +20816,12 @@
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT120" t="n">
@@ -20743,47 +20829,47 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -20810,17 +20896,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -20854,170 +20940,81 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>20</v>
+        <v>262</v>
       </c>
       <c r="O121" t="n">
-        <v>20</v>
-      </c>
-      <c r="U121" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V121" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X121" t="inlineStr">
-        <is>
-          <t>Tuberkulose</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA121" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD121" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE121" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF121" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG121" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
-        </is>
-      </c>
-      <c r="AM121" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN121" t="b">
-        <v>1</v>
+        <v>262</v>
+      </c>
+      <c r="R121" t="n">
+        <v>3.550808134115378</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ121" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS121" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -21049,12 +21046,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21088,13 +21085,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="O122" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="R122" t="n">
-        <v>0.8132420005828864</v>
+        <v>0.3537951651591013</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -21103,7 +21100,7 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -21128,7 +21125,7 @@
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT122" t="n">
@@ -21141,42 +21138,42 @@
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21208,12 +21205,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21247,29 +21244,29 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="O123" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>Tuberculosis disease</t>
+          <t>Tuberkulose</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
@@ -21279,7 +21276,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -21294,7 +21291,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
@@ -21329,17 +21326,17 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly tuberculosis disease notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
         </is>
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -21362,7 +21359,7 @@
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT123" t="n">
@@ -21375,42 +21372,42 @@
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21442,12 +21439,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21481,13 +21478,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="O124" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="R124" t="n">
-        <v>0.2336220107070837</v>
+        <v>0.8132420005828864</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -21496,7 +21493,7 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -21521,7 +21518,7 @@
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT124" t="n">
@@ -21534,42 +21531,42 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21601,12 +21598,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -21640,29 +21637,29 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="O125" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>Tuberkulos</t>
+          <t>Tuberculosis disease</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -21672,7 +21669,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -21687,7 +21684,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
@@ -21722,17 +21719,17 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
+          <t>New Zealand PHF Science monthly tuberculosis disease notifications.</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -21755,7 +21752,7 @@
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT125" t="n">
@@ -21768,42 +21765,42 @@
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21835,12 +21832,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -21865,7 +21862,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -21874,81 +21871,95 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>273</v>
+        <v>25</v>
       </c>
       <c r="O126" t="n">
-        <v>273</v>
+        <v>25</v>
       </c>
       <c r="R126" t="n">
-        <v>0.2229886952654542</v>
+        <v>0.2336220107070837</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21975,17 +21986,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22010,7 +22021,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -22019,81 +22030,170 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="O127" t="n">
-        <v>84</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0.02406632031526284</v>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>25</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Tuberkulos</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22155,7 +22255,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -22164,13 +22264,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="O128" t="n">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="R128" t="n">
-        <v>0.2213550784503227</v>
+        <v>0.2229886952654542</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -22300,7 +22400,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -22309,13 +22409,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="O129" t="n">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="R129" t="n">
-        <v>0.01948225930283182</v>
+        <v>0.02406632031526284</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -22445,7 +22545,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -22454,13 +22554,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="O130" t="n">
-        <v>229</v>
+        <v>271</v>
       </c>
       <c r="R130" t="n">
-        <v>0.1870491253325605</v>
+        <v>0.2213550784503227</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -22590,7 +22690,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -22599,13 +22699,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="O131" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="R131" t="n">
-        <v>0.01461169447712387</v>
+        <v>0.01948225930283182</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -22735,7 +22835,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -22744,13 +22844,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>265</v>
+        <v>229</v>
       </c>
       <c r="O132" t="n">
-        <v>265</v>
+        <v>229</v>
       </c>
       <c r="R132" t="n">
-        <v>0.2164542280049281</v>
+        <v>0.1870491253325605</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -22880,7 +22980,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -22889,13 +22989,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="O133" t="n">
-        <v>93</v>
+        <v>51</v>
       </c>
       <c r="R133" t="n">
-        <v>0.02664485463475528</v>
+        <v>0.01461169447712387</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -22995,12 +23095,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -23025,22 +23125,22 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>152</v>
+        <v>265</v>
       </c>
       <c r="O134" t="n">
-        <v>152</v>
+        <v>265</v>
       </c>
       <c r="R134" t="n">
-        <v>0.5582673965670081</v>
+        <v>0.2164542280049281</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23073,42 +23173,42 @@
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23140,12 +23240,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -23170,104 +23270,90 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="O135" t="n">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="R135" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.02664485463475528</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23294,17 +23380,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23338,170 +23424,81 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>11</v>
+        <v>152</v>
       </c>
       <c r="O136" t="n">
-        <v>11</v>
-      </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>Tuberculosis, total</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr">
+        <v>152</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.5582673965670081</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP136" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
+      <c r="AT136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV136" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN136" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP136" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AT136" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV136" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23533,12 +23530,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23572,13 +23569,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O137" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R137" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -23587,7 +23584,7 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -23607,12 +23604,12 @@
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT137" t="n">
@@ -23620,47 +23617,47 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23692,12 +23689,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -23731,29 +23728,29 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O138" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>Tuberkulose</t>
+          <t>Tuberculosis, total</t>
         </is>
       </c>
       <c r="Y138" t="inlineStr">
@@ -23778,7 +23775,7 @@
       </c>
       <c r="AC138" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD138" t="inlineStr">
@@ -23813,17 +23810,17 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -23841,12 +23838,12 @@
       </c>
       <c r="AQ138" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT138" t="n">
@@ -23854,47 +23851,47 @@
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23926,12 +23923,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23965,13 +23962,13 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="O139" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="R139" t="n">
-        <v>0.242966891135367</v>
+        <v>0.08844879128977531</v>
       </c>
       <c r="S139" t="inlineStr">
         <is>
@@ -23980,7 +23977,7 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -24005,7 +24002,7 @@
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT139" t="n">
@@ -24018,42 +24015,42 @@
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24085,12 +24082,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -24124,29 +24121,29 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="O140" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>Tuberkulos</t>
+          <t>Tuberkulose</t>
         </is>
       </c>
       <c r="Y140" t="inlineStr">
@@ -24171,7 +24168,7 @@
       </c>
       <c r="AC140" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD140" t="inlineStr">
@@ -24206,17 +24203,17 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
         </is>
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -24239,7 +24236,7 @@
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT140" t="n">
@@ -24252,42 +24249,42 @@
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24319,12 +24316,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24349,7 +24346,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -24358,81 +24355,95 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>213</v>
+        <v>26</v>
       </c>
       <c r="O141" t="n">
-        <v>213</v>
+        <v>26</v>
       </c>
       <c r="R141" t="n">
-        <v>0.1739801908115082</v>
+        <v>0.242966891135367</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24459,17 +24470,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24494,7 +24505,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -24503,81 +24514,170 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="O142" t="n">
-        <v>62</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0.01776323642317019</v>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Tuberkulos</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN142" t="b">
+        <v>1</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24639,7 +24739,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -24648,13 +24748,13 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="O143" t="n">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="R143" t="n">
-        <v>0.1894995505552578</v>
+        <v>0.1739801908115082</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
@@ -24784,7 +24884,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -24793,13 +24893,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="O144" t="n">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="R144" t="n">
-        <v>0.03237493090029405</v>
+        <v>0.01776323642317019</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -24929,7 +25029,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -24938,13 +25038,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="O145" t="n">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="R145" t="n">
-        <v>0.2017516766687443</v>
+        <v>0.1894995505552578</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -25074,7 +25174,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -25083,13 +25183,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="O146" t="n">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="R146" t="n">
-        <v>0.01833624404972407</v>
+        <v>0.03237493090029405</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -25219,7 +25319,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -25228,13 +25328,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O147" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="R147" t="n">
-        <v>0.199301251446047</v>
+        <v>0.2017516766687443</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -25364,7 +25464,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -25373,13 +25473,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="O148" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="R148" t="n">
-        <v>0.02148778599577039</v>
+        <v>0.01833624404972407</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -25509,7 +25609,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25518,13 +25618,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="O149" t="n">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="R149" t="n">
-        <v>0.1837818917022974</v>
+        <v>0.199301251446047</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25624,12 +25724,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25654,22 +25754,22 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N150" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="O150" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="R150" t="n">
-        <v>0.1836405909759895</v>
+        <v>0.02148778599577039</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -25702,42 +25802,42 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25769,12 +25869,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -25799,104 +25899,90 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N151" t="n">
-        <v>3</v>
+        <v>225</v>
       </c>
       <c r="O151" t="n">
-        <v>3</v>
+        <v>225</v>
       </c>
       <c r="R151" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.1837818917022974</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AA151" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ151" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS151" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR151" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25923,17 +26009,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -25967,170 +26053,81 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="O152" t="n">
-        <v>3</v>
-      </c>
-      <c r="U152" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="V152" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="W152" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X152" t="inlineStr">
-        <is>
-          <t>Tuberculosis, total</t>
-        </is>
-      </c>
-      <c r="Y152" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA152" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD152" t="inlineStr">
+        <v>53</v>
+      </c>
+      <c r="R152" t="n">
+        <v>0.1946590264345489</v>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR152" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr"/>
+      <c r="AT152" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE152" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF152" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG152" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH152" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI152" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM152" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN152" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP152" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ152" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AT152" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV152" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -26162,12 +26159,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -26201,13 +26198,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O153" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R153" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26216,7 +26213,7 @@
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -26236,12 +26233,12 @@
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT153" t="n">
@@ -26249,47 +26246,47 @@
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26321,12 +26318,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26360,29 +26357,29 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="V154" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="W154" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>Tuberkulose</t>
+          <t>Tuberculosis, total</t>
         </is>
       </c>
       <c r="Y154" t="inlineStr">
@@ -26407,7 +26404,7 @@
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD154" t="inlineStr">
@@ -26442,17 +26439,17 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -26470,12 +26467,12 @@
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT154" t="n">
@@ -26483,47 +26480,47 @@
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26555,12 +26552,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -26594,81 +26591,95 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="O155" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="R155" t="n">
-        <v>0.02062827455593957</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -26695,17 +26706,17 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26730,7 +26741,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -26739,81 +26750,170 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>272</v>
+        <v>1</v>
       </c>
       <c r="O156" t="n">
-        <v>272</v>
-      </c>
-      <c r="R156" t="n">
-        <v>0.2221718868578884</v>
-      </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD156" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE156" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF156" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG156" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH156" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM156" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN156" t="b">
+        <v>1</v>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ156" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -26875,7 +26975,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -26884,13 +26984,13 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="O157" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="R157" t="n">
-        <v>0.02950989276752467</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
@@ -26957,6 +27057,296 @@
         </is>
       </c>
       <c r="BC157" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N158" t="n">
+        <v>272</v>
+      </c>
+      <c r="O158" t="n">
+        <v>272</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0.2221718868578884</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP158" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR158" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr"/>
+      <c r="AT158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU158" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV158" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW158" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX158" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA158" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB158" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC158" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N159" t="n">
+        <v>103</v>
+      </c>
+      <c r="O159" t="n">
+        <v>103</v>
+      </c>
+      <c r="R159" t="n">
+        <v>0.02950989276752467</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP159" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR159" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr"/>
+      <c r="AT159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU159" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV159" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA159" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB159" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC159" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -27078,7 +27468,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10">
@@ -27088,7 +27478,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -27108,7 +27498,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -27140,7 +27530,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>348123</v>
+        <v>348202</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -23424,13 +23424,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O136" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R136" t="n">
-        <v>0.5582673965670081</v>
+        <v>0.5545945847474882</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -26053,13 +26053,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="O152" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="R152" t="n">
-        <v>0.1946590264345489</v>
+        <v>0.209350273712628</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -27349,6 +27349,151 @@
       <c r="BC159" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N160" t="n">
+        <v>249</v>
+      </c>
+      <c r="O160" t="n">
+        <v>249</v>
+      </c>
+      <c r="R160" t="n">
+        <v>0.2033852934838758</v>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP160" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
+      <c r="AT160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU160" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV160" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27385,7 +27530,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -27468,7 +27613,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="10">
@@ -27478,7 +27623,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11">
@@ -27530,7 +27675,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>348202</v>
+        <v>348454</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -23530,12 +23530,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23569,95 +23569,84 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>11</v>
+        <v>58871</v>
       </c>
       <c r="O137" t="n">
-        <v>11</v>
+        <v>58871</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>190</v>
       </c>
       <c r="R137" t="n">
-        <v>0.1956690087950551</v>
+        <v>4.166636915801409</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -23684,7 +23673,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -23733,98 +23722,23 @@
       <c r="O138" t="n">
         <v>11</v>
       </c>
+      <c r="R138" t="n">
+        <v>0.1956690087950551</v>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U138" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
-      <c r="V138" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="W138" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X138" t="inlineStr">
-        <is>
-          <t>Tuberculosis, total</t>
-        </is>
-      </c>
-      <c r="Y138" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD138" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE138" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF138" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG138" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM138" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN138" t="b">
-        <v>1</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -23918,17 +23832,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23962,22 +23876,39 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O139" t="n">
-        <v>5</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0.08844879128977531</v>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>11</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Tuberculosis, total</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -23985,6 +23916,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -23997,12 +23986,12 @@
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT139" t="n">
@@ -24010,47 +23999,47 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24077,7 +24066,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -24126,98 +24115,23 @@
       <c r="O140" t="n">
         <v>5</v>
       </c>
+      <c r="R140" t="n">
+        <v>0.08844879128977531</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U140" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>Tuberkulose</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD140" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE140" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF140" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG140" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN140" t="b">
-        <v>1</v>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
@@ -24311,17 +24225,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24355,22 +24269,39 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="O141" t="n">
-        <v>26</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0.242966891135367</v>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>5</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -24378,6 +24309,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN141" t="b">
+        <v>1</v>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -24395,7 +24384,7 @@
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT141" t="n">
@@ -24408,42 +24397,42 @@
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24470,7 +24459,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -24519,98 +24508,23 @@
       <c r="O142" t="n">
         <v>26</v>
       </c>
+      <c r="R142" t="n">
+        <v>0.242966891135367</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U142" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
         </is>
       </c>
-      <c r="V142" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
-        </is>
-      </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>Tuberkulos</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD142" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE142" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF142" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG142" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ142" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK142" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
-        </is>
-      </c>
-      <c r="AM142" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN142" t="b">
-        <v>1</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
@@ -24704,17 +24618,17 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24739,7 +24653,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -24748,81 +24662,170 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>213</v>
+        <v>26</v>
       </c>
       <c r="O143" t="n">
-        <v>213</v>
-      </c>
-      <c r="R143" t="n">
-        <v>0.1739801908115082</v>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>Tuberkulos</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN143" t="b">
+        <v>1</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24854,12 +24857,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24893,13 +24896,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>62</v>
+        <v>213</v>
       </c>
       <c r="O144" t="n">
-        <v>62</v>
+        <v>213</v>
       </c>
       <c r="R144" t="n">
-        <v>0.01776323642317019</v>
+        <v>0.1739801908115082</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -24932,42 +24935,42 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24999,12 +25002,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -25029,7 +25032,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -25038,13 +25041,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>232</v>
+        <v>62</v>
       </c>
       <c r="O145" t="n">
-        <v>232</v>
+        <v>62</v>
       </c>
       <c r="R145" t="n">
-        <v>0.1894995505552578</v>
+        <v>0.01776323642317019</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -25077,42 +25080,42 @@
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25144,12 +25147,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -25183,13 +25186,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>113</v>
+        <v>232</v>
       </c>
       <c r="O146" t="n">
-        <v>113</v>
+        <v>232</v>
       </c>
       <c r="R146" t="n">
-        <v>0.03237493090029405</v>
+        <v>0.1894995505552578</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -25222,42 +25225,42 @@
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25289,12 +25292,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -25319,7 +25322,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -25328,13 +25331,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>247</v>
+        <v>113</v>
       </c>
       <c r="O147" t="n">
-        <v>247</v>
+        <v>113</v>
       </c>
       <c r="R147" t="n">
-        <v>0.2017516766687443</v>
+        <v>0.03237493090029405</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -25367,42 +25370,42 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25434,12 +25437,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -25473,13 +25476,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>64</v>
+        <v>247</v>
       </c>
       <c r="O148" t="n">
-        <v>64</v>
+        <v>247</v>
       </c>
       <c r="R148" t="n">
-        <v>0.01833624404972407</v>
+        <v>0.2017516766687443</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -25512,42 +25515,42 @@
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25579,12 +25582,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25609,7 +25612,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25618,13 +25621,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>244</v>
+        <v>64</v>
       </c>
       <c r="O149" t="n">
-        <v>244</v>
+        <v>64</v>
       </c>
       <c r="R149" t="n">
-        <v>0.199301251446047</v>
+        <v>0.01833624404972407</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25657,42 +25660,42 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25724,12 +25727,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25763,13 +25766,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>75</v>
+        <v>244</v>
       </c>
       <c r="O150" t="n">
-        <v>75</v>
+        <v>244</v>
       </c>
       <c r="R150" t="n">
-        <v>0.02148778599577039</v>
+        <v>0.199301251446047</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -25802,42 +25805,42 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25869,12 +25872,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -25899,7 +25902,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25908,13 +25911,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="O151" t="n">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="R151" t="n">
-        <v>0.1837818917022974</v>
+        <v>0.02148778599577039</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -25947,42 +25950,42 @@
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26014,12 +26017,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -26044,22 +26047,22 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N152" t="n">
-        <v>57</v>
+        <v>225</v>
       </c>
       <c r="O152" t="n">
-        <v>57</v>
+        <v>225</v>
       </c>
       <c r="R152" t="n">
-        <v>0.209350273712628</v>
+        <v>0.1837818917022974</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -26092,42 +26095,42 @@
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26159,12 +26162,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -26198,95 +26201,81 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="O153" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="R153" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.209350273712628</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ153" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -26313,7 +26302,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -26362,98 +26351,23 @@
       <c r="O154" t="n">
         <v>3</v>
       </c>
+      <c r="R154" t="n">
+        <v>0.05336427512592412</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U154" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>Tuberculosis, total</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE154" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF154" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG154" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN154" t="b">
-        <v>1</v>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
@@ -26547,17 +26461,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -26591,29 +26505,104 @@
         </is>
       </c>
       <c r="N155" t="n">
+        <v>3</v>
+      </c>
+      <c r="O155" t="n">
+        <v>3</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Tuberculosis, total</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
         <v>1</v>
       </c>
-      <c r="O155" t="n">
-        <v>1</v>
-      </c>
-      <c r="R155" t="n">
-        <v>0.01768975825795506</v>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -26626,12 +26615,12 @@
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT155" t="n">
@@ -26639,47 +26628,47 @@
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26706,7 +26695,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -26755,98 +26744,23 @@
       <c r="O156" t="n">
         <v>1</v>
       </c>
+      <c r="R156" t="n">
+        <v>0.01768975825795506</v>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U156" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
-      <c r="V156" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X156" t="inlineStr">
-        <is>
-          <t>Tuberkulose</t>
-        </is>
-      </c>
-      <c r="Y156" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD156" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE156" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF156" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG156" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ156" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK156" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
-        </is>
-      </c>
-      <c r="AM156" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN156" t="b">
-        <v>1</v>
       </c>
       <c r="AO156" t="inlineStr">
         <is>
@@ -26940,17 +26854,17 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26984,81 +26898,170 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="O157" t="n">
-        <v>72</v>
-      </c>
-      <c r="R157" t="n">
-        <v>0.02062827455593957</v>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U157" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD157" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE157" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF157" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG157" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM157" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN157" t="b">
+        <v>1</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ157" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27090,12 +27093,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -27120,7 +27123,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -27129,13 +27132,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>272</v>
+        <v>72</v>
       </c>
       <c r="O158" t="n">
-        <v>272</v>
+        <v>72</v>
       </c>
       <c r="R158" t="n">
-        <v>0.2221718868578884</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -27168,42 +27171,42 @@
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27235,12 +27238,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -27265,7 +27268,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -27274,13 +27277,13 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>103</v>
+        <v>272</v>
       </c>
       <c r="O159" t="n">
-        <v>103</v>
+        <v>272</v>
       </c>
       <c r="R159" t="n">
-        <v>0.02950989276752467</v>
+        <v>0.2221718868578884</v>
       </c>
       <c r="S159" t="inlineStr">
         <is>
@@ -27313,42 +27316,42 @@
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27380,12 +27383,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27410,7 +27413,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -27419,13 +27422,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>249</v>
+        <v>103</v>
       </c>
       <c r="O160" t="n">
-        <v>249</v>
+        <v>103</v>
       </c>
       <c r="R160" t="n">
-        <v>0.2033852934838758</v>
+        <v>0.02950989276752467</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -27458,40 +27461,185 @@
       </c>
       <c r="AV160" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA160" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB160" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC160" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N161" t="n">
+        <v>249</v>
+      </c>
+      <c r="O161" t="n">
+        <v>249</v>
+      </c>
+      <c r="R161" t="n">
+        <v>0.2033852934838758</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP161" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR161" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS161" t="inlineStr"/>
+      <c r="AT161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU161" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV161" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW160" t="inlineStr">
+      <c r="AW161" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX160" t="inlineStr">
+      <c r="AX161" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY160" t="inlineStr">
+      <c r="AY161" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ160" t="inlineStr">
+      <c r="AZ161" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA160" t="inlineStr">
+      <c r="BA161" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB160" t="inlineStr">
+      <c r="BB161" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC160" t="inlineStr">
+      <c r="BC161" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -27613,7 +27761,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="10">
@@ -27623,7 +27771,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -27675,7 +27823,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>348454</v>
+        <v>407325</v>
       </c>
     </row>
     <row r="16">
@@ -27685,7 +27833,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1001</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -26201,13 +26201,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="O153" t="n">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="R153" t="n">
-        <v>0.209350273712628</v>
+        <v>0.2497512037273457</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26739,13 +26739,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O156" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R156" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26898,10 +26898,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -27642,6 +27642,151 @@
       <c r="BC161" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N162" t="n">
+        <v>68</v>
+      </c>
+      <c r="O162" t="n">
+        <v>68</v>
+      </c>
+      <c r="R162" t="n">
+        <v>0.01948225930283182</v>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP162" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR162" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr"/>
+      <c r="AT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV162" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA162" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB162" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC162" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27678,7 +27823,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -27761,7 +27906,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
@@ -27771,7 +27916,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11">
@@ -27823,7 +27968,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>407325</v>
+        <v>407406</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -23424,13 +23424,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="O136" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="R136" t="n">
-        <v>0.5545945847474882</v>
+        <v>0.5582673965670081</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -26201,13 +26201,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="O153" t="n">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="R153" t="n">
-        <v>0.2497512037273457</v>
+        <v>0.2901521337420634</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26346,13 +26346,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O154" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R154" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26505,10 +26505,10 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O155" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>407406</v>
+        <v>407419</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -26201,13 +26201,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O153" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R153" t="n">
-        <v>0.2901521337420634</v>
+        <v>0.2938249455615832</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>407419</v>
+        <v>407420</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -21478,13 +21478,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O124" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R124" t="n">
-        <v>0.8132420005828864</v>
+        <v>0.7754167912534499</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -21637,10 +21637,10 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="O125" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -23424,13 +23424,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="O136" t="n">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="R136" t="n">
-        <v>0.5582673965670081</v>
+        <v>0.5545945847474882</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23717,13 +23717,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O138" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R138" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.2134571005036965</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -23876,10 +23876,10 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O139" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
@@ -24110,13 +24110,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O140" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R140" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.1061385495477304</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -24269,10 +24269,10 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O141" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U141" t="inlineStr">
         <is>
@@ -24464,12 +24464,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24503,13 +24503,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="O142" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="R142" t="n">
-        <v>0.242966891135367</v>
+        <v>0.6619411632651402</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -24543,7 +24543,7 @@
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT142" t="n">
@@ -24556,42 +24556,42 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24623,12 +24623,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24662,29 +24662,29 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="O143" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>Tuberkulos</t>
+          <t>Tuberculosis disease</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
@@ -24694,7 +24694,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -24709,7 +24709,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr">
@@ -24744,17 +24744,17 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
+          <t>New Zealand PHF Science monthly tuberculosis disease notifications.</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -24777,7 +24777,7 @@
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT143" t="n">
@@ -24790,42 +24790,42 @@
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24857,12 +24857,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24887,7 +24887,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -24896,81 +24896,95 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>213</v>
+        <v>26</v>
       </c>
       <c r="O144" t="n">
-        <v>213</v>
+        <v>26</v>
       </c>
       <c r="R144" t="n">
-        <v>0.1739801908115082</v>
+        <v>0.242966891135367</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24997,17 +25011,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -25032,7 +25046,7 @@
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
@@ -25041,81 +25055,170 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="O145" t="n">
-        <v>62</v>
-      </c>
-      <c r="R145" t="n">
-        <v>0.01776323642317019</v>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>Tuberkulos</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN145" t="b">
+        <v>1</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25177,7 +25280,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -25186,13 +25289,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="O146" t="n">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="R146" t="n">
-        <v>0.1894995505552578</v>
+        <v>0.1739801908115082</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -25322,7 +25425,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -25331,13 +25434,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="O147" t="n">
-        <v>113</v>
+        <v>62</v>
       </c>
       <c r="R147" t="n">
-        <v>0.03237493090029405</v>
+        <v>0.01776323642317019</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -25467,7 +25570,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -25476,13 +25579,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="O148" t="n">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="R148" t="n">
-        <v>0.2017516766687443</v>
+        <v>0.1894995505552578</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -25612,7 +25715,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25621,13 +25724,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="O149" t="n">
-        <v>64</v>
+        <v>113</v>
       </c>
       <c r="R149" t="n">
-        <v>0.01833624404972407</v>
+        <v>0.03237493090029405</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25757,7 +25860,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25766,13 +25869,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="O150" t="n">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="R150" t="n">
-        <v>0.199301251446047</v>
+        <v>0.2017516766687443</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -25902,7 +26005,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25911,13 +26014,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="O151" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="R151" t="n">
-        <v>0.02148778599577039</v>
+        <v>0.01833624404972407</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -26047,7 +26150,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -26056,13 +26159,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="O152" t="n">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="R152" t="n">
-        <v>0.1837818917022974</v>
+        <v>0.199301251446047</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -26162,12 +26265,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -26192,22 +26295,22 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N153" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="O153" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="R153" t="n">
-        <v>0.2938249455615832</v>
+        <v>0.02148778599577039</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26240,42 +26343,42 @@
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26307,12 +26410,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26337,104 +26440,90 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N154" t="n">
-        <v>4</v>
+        <v>225</v>
       </c>
       <c r="O154" t="n">
-        <v>4</v>
+        <v>225</v>
       </c>
       <c r="R154" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.1837818917022974</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AA154" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ154" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS154" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR154" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26461,17 +26550,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -26505,170 +26594,81 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="O155" t="n">
-        <v>4</v>
-      </c>
-      <c r="U155" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="V155" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="W155" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X155" t="inlineStr">
-        <is>
-          <t>Tuberculosis, total</t>
-        </is>
-      </c>
-      <c r="Y155" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA155" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC155" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD155" t="inlineStr">
+        <v>93</v>
+      </c>
+      <c r="R155" t="n">
+        <v>0.3415714992153405</v>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO155" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP155" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR155" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr"/>
+      <c r="AT155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU155" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV155" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE155" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF155" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG155" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ155" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK155" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM155" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN155" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP155" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ155" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AT155" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV155" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -26700,12 +26700,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26739,13 +26739,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O156" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R156" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -26774,12 +26774,12 @@
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT156" t="n">
@@ -26787,47 +26787,47 @@
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -26859,12 +26859,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26898,29 +26898,29 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O157" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>Tuberkulose</t>
+          <t>Tuberculosis, total</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
@@ -26945,7 +26945,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD157" t="inlineStr">
@@ -26980,17 +26980,17 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -27008,12 +27008,12 @@
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT157" t="n">
@@ -27021,47 +27021,47 @@
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27093,12 +27093,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -27132,81 +27132,95 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="O158" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="R158" t="n">
-        <v>0.02062827455593957</v>
+        <v>0.07075903303182025</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS158" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ158" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS158" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27233,17 +27247,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -27268,7 +27282,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -27277,81 +27291,170 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>272</v>
+        <v>4</v>
       </c>
       <c r="O159" t="n">
-        <v>272</v>
-      </c>
-      <c r="R159" t="n">
-        <v>0.2221718868578884</v>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27413,7 +27516,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -27422,13 +27525,13 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="O160" t="n">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="R160" t="n">
-        <v>0.02950989276752467</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -27558,7 +27661,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -27567,13 +27670,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="O161" t="n">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="R161" t="n">
-        <v>0.2033852934838758</v>
+        <v>0.2221718868578884</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -27703,7 +27806,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -27712,13 +27815,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="O162" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="R162" t="n">
-        <v>0.01948225930283182</v>
+        <v>0.02950989276752467</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -27787,6 +27890,441 @@
       <c r="BC162" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N163" t="n">
+        <v>249</v>
+      </c>
+      <c r="O163" t="n">
+        <v>249</v>
+      </c>
+      <c r="R163" t="n">
+        <v>0.2033852934838758</v>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP163" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR163" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
+      <c r="AT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV163" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW163" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX163" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY163" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA163" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB163" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC163" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N164" t="n">
+        <v>68</v>
+      </c>
+      <c r="O164" t="n">
+        <v>68</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0.01948225930283182</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW164" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX164" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY164" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA164" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB164" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC164" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N165" t="n">
+        <v>185</v>
+      </c>
+      <c r="O165" t="n">
+        <v>185</v>
+      </c>
+      <c r="R165" t="n">
+        <v>0.1511095553996668</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP165" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR165" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS165" t="inlineStr"/>
+      <c r="AT165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU165" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV165" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW165" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX165" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY165" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA165" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB165" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC165" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27823,7 +28361,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -27906,7 +28444,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10">
@@ -27916,7 +28454,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -27936,7 +28474,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -27968,7 +28506,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>407420</v>
+        <v>407654</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -26594,13 +26594,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="O155" t="n">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="R155" t="n">
-        <v>0.3415714992153405</v>
+        <v>0.3929908646886175</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>407654</v>
+        <v>407668</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -26739,13 +26739,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O156" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R156" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.1067285502518482</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26898,10 +26898,10 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O157" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -28325,6 +28325,151 @@
       <c r="BC165" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N166" t="n">
+        <v>72</v>
+      </c>
+      <c r="O166" t="n">
+        <v>72</v>
+      </c>
+      <c r="R166" t="n">
+        <v>0.02062827455593957</v>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP166" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR166" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr"/>
+      <c r="AT166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU166" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV166" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28361,7 +28506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -28444,7 +28589,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10">
@@ -28454,7 +28599,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -28506,7 +28651,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>407668</v>
+        <v>407741</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -24071,12 +24071,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -24110,95 +24110,81 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>6</v>
+        <v>279</v>
       </c>
       <c r="O140" t="n">
-        <v>6</v>
+        <v>279</v>
       </c>
       <c r="R140" t="n">
-        <v>0.1061385495477304</v>
+        <v>3.78120408174882</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24225,7 +24211,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -24274,98 +24260,23 @@
       <c r="O141" t="n">
         <v>6</v>
       </c>
+      <c r="R141" t="n">
+        <v>0.1061385495477304</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U141" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
-      <c r="V141" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X141" t="inlineStr">
-        <is>
-          <t>Tuberkulose</t>
-        </is>
-      </c>
-      <c r="Y141" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD141" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE141" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF141" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG141" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK141" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN141" t="b">
-        <v>1</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
@@ -24459,17 +24370,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -24503,22 +24414,39 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="O142" t="n">
-        <v>35</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0.6619411632651402</v>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -24526,6 +24454,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN142" t="b">
+        <v>1</v>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -24543,7 +24529,7 @@
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
       <c r="AT142" t="n">
@@ -24556,42 +24542,42 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24618,7 +24604,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -24667,98 +24653,23 @@
       <c r="O143" t="n">
         <v>35</v>
       </c>
+      <c r="R143" t="n">
+        <v>0.6619411632651402</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U143" t="inlineStr">
         <is>
           <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
-      <c r="V143" t="inlineStr">
-        <is>
-          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>Tuberculosis disease</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD143" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE143" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF143" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG143" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK143" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly tuberculosis disease notifications.</t>
-        </is>
-      </c>
-      <c r="AM143" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN143" t="b">
-        <v>1</v>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
@@ -24852,17 +24763,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24896,22 +24807,39 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="O144" t="n">
-        <v>26</v>
-      </c>
-      <c r="R144" t="n">
-        <v>0.242966891135367</v>
-      </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>35</v>
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>Tuberculosis disease</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -24919,6 +24847,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly tuberculosis disease notifications.</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN144" t="b">
+        <v>1</v>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -24936,7 +24922,7 @@
       </c>
       <c r="AS144" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+          <t>SER_NZ_TUBERCULOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT144" t="n">
@@ -24949,42 +24935,42 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25011,7 +24997,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -25060,98 +25046,23 @@
       <c r="O145" t="n">
         <v>26</v>
       </c>
+      <c r="R145" t="n">
+        <v>0.242966891135367</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U145" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
         </is>
       </c>
-      <c r="V145" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
-        </is>
-      </c>
-      <c r="W145" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X145" t="inlineStr">
-        <is>
-          <t>Tuberkulos</t>
-        </is>
-      </c>
-      <c r="Y145" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z145" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB145" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD145" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE145" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF145" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG145" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
-        </is>
-      </c>
-      <c r="AM145" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN145" t="b">
-        <v>1</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
@@ -25245,17 +25156,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -25280,7 +25191,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -25289,81 +25200,170 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>213</v>
+        <v>26</v>
       </c>
       <c r="O146" t="n">
-        <v>213</v>
-      </c>
-      <c r="R146" t="n">
-        <v>0.1739801908115082</v>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>26</v>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>Tuberkulos</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM tuberculosis disease category.</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN146" t="b">
+        <v>1</v>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS146" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_TUBERCULOSIS</t>
+        </is>
+      </c>
       <c r="AT146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25395,12 +25395,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -25434,13 +25434,13 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>62</v>
+        <v>213</v>
       </c>
       <c r="O147" t="n">
-        <v>62</v>
+        <v>213</v>
       </c>
       <c r="R147" t="n">
-        <v>0.01776323642317019</v>
+        <v>0.1739801908115082</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
@@ -25473,42 +25473,42 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25540,12 +25540,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -25570,7 +25570,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -25579,13 +25579,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>232</v>
+        <v>62</v>
       </c>
       <c r="O148" t="n">
-        <v>232</v>
+        <v>62</v>
       </c>
       <c r="R148" t="n">
-        <v>0.1894995505552578</v>
+        <v>0.01776323642317019</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -25618,42 +25618,42 @@
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25685,12 +25685,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -25724,13 +25724,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>113</v>
+        <v>232</v>
       </c>
       <c r="O149" t="n">
-        <v>113</v>
+        <v>232</v>
       </c>
       <c r="R149" t="n">
-        <v>0.03237493090029405</v>
+        <v>0.1894995505552578</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25763,42 +25763,42 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25830,12 +25830,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -25860,7 +25860,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25869,13 +25869,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>247</v>
+        <v>113</v>
       </c>
       <c r="O150" t="n">
-        <v>247</v>
+        <v>113</v>
       </c>
       <c r="R150" t="n">
-        <v>0.2017516766687443</v>
+        <v>0.03237493090029405</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -25908,42 +25908,42 @@
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25975,12 +25975,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -26014,13 +26014,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>64</v>
+        <v>247</v>
       </c>
       <c r="O151" t="n">
-        <v>64</v>
+        <v>247</v>
       </c>
       <c r="R151" t="n">
-        <v>0.01833624404972407</v>
+        <v>0.2017516766687443</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -26053,42 +26053,42 @@
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26120,12 +26120,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -26150,7 +26150,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -26159,13 +26159,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>244</v>
+        <v>64</v>
       </c>
       <c r="O152" t="n">
-        <v>244</v>
+        <v>64</v>
       </c>
       <c r="R152" t="n">
-        <v>0.199301251446047</v>
+        <v>0.01833624404972407</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -26198,42 +26198,42 @@
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26265,12 +26265,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -26304,13 +26304,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>75</v>
+        <v>244</v>
       </c>
       <c r="O153" t="n">
-        <v>75</v>
+        <v>244</v>
       </c>
       <c r="R153" t="n">
-        <v>0.02148778599577039</v>
+        <v>0.199301251446047</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -26343,42 +26343,42 @@
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26410,12 +26410,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -26440,7 +26440,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -26449,13 +26449,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="O154" t="n">
-        <v>225</v>
+        <v>75</v>
       </c>
       <c r="R154" t="n">
-        <v>0.1837818917022974</v>
+        <v>0.02148778599577039</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -26488,42 +26488,42 @@
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26555,12 +26555,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -26585,22 +26585,22 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N155" t="n">
-        <v>107</v>
+        <v>225</v>
       </c>
       <c r="O155" t="n">
-        <v>107</v>
+        <v>225</v>
       </c>
       <c r="R155" t="n">
-        <v>0.3929908646886175</v>
+        <v>0.1837818917022974</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -26633,42 +26633,42 @@
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26700,12 +26700,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26739,95 +26739,81 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="O156" t="n">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="R156" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.4113549237862165</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="AA156" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ156" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS156" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR156" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -26854,7 +26840,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -26903,98 +26889,23 @@
       <c r="O157" t="n">
         <v>6</v>
       </c>
+      <c r="R157" t="n">
+        <v>0.1067285502518482</v>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U157" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
-      <c r="V157" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_700</t>
-        </is>
-      </c>
-      <c r="W157" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X157" t="inlineStr">
-        <is>
-          <t>Tuberculosis, total</t>
-        </is>
-      </c>
-      <c r="Y157" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD157" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE157" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF157" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG157" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ157" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK157" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
-        </is>
-      </c>
-      <c r="AM157" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN157" t="b">
-        <v>1</v>
       </c>
       <c r="AO157" t="inlineStr">
         <is>
@@ -27088,17 +26999,17 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -27132,22 +27043,39 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O158" t="n">
-        <v>4</v>
-      </c>
-      <c r="R158" t="n">
-        <v>0.07075903303182025</v>
-      </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_700</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>Tuberculosis, total</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -27155,6 +27083,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD158" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE158" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF158" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG158" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Use the THL reported total only; pulmonary and other-organ child rows remain independent unprojected series.</t>
+        </is>
+      </c>
+      <c r="AM158" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN158" t="b">
+        <v>1</v>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -27167,12 +27153,12 @@
       </c>
       <c r="AQ158" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
+          <t>SER_FI_THL_TTR_700</t>
         </is>
       </c>
       <c r="AT158" t="n">
@@ -27180,47 +27166,47 @@
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27247,7 +27233,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -27296,98 +27282,23 @@
       <c r="O159" t="n">
         <v>4</v>
       </c>
+      <c r="R159" t="n">
+        <v>0.07075903303182025</v>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U159" t="inlineStr">
         <is>
           <t>SER_NO_FHI_102_MONTHLY</t>
         </is>
       </c>
-      <c r="V159" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_102_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X159" t="inlineStr">
-        <is>
-          <t>Tuberkulose</t>
-        </is>
-      </c>
-      <c r="Y159" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD159" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE159" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF159" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG159" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH159" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI159" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ159" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK159" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
-        </is>
-      </c>
-      <c r="AM159" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN159" t="b">
-        <v>1</v>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
@@ -27481,17 +27392,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -27525,81 +27436,170 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="O160" t="n">
-        <v>72</v>
-      </c>
-      <c r="R160" t="n">
-        <v>0.02062827455593957</v>
-      </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>Tuberkulose</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD160" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE160" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF160" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG160" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH160" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI160" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS disease mapping; excludes preventive treatment.</t>
+        </is>
+      </c>
+      <c r="AM160" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN160" t="b">
+        <v>1</v>
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ160" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_102_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -27631,12 +27631,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -27661,7 +27661,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -27670,13 +27670,13 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>272</v>
+        <v>72</v>
       </c>
       <c r="O161" t="n">
-        <v>272</v>
+        <v>72</v>
       </c>
       <c r="R161" t="n">
-        <v>0.2221718868578884</v>
+        <v>0.02062827455593957</v>
       </c>
       <c r="S161" t="inlineStr">
         <is>
@@ -27709,42 +27709,42 @@
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27776,12 +27776,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -27806,7 +27806,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
@@ -27815,13 +27815,13 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>103</v>
+        <v>272</v>
       </c>
       <c r="O162" t="n">
-        <v>103</v>
+        <v>272</v>
       </c>
       <c r="R162" t="n">
-        <v>0.02950989276752467</v>
+        <v>0.2221718868578884</v>
       </c>
       <c r="S162" t="inlineStr">
         <is>
@@ -27854,42 +27854,42 @@
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27921,12 +27921,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -27951,7 +27951,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -27960,13 +27960,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>249</v>
+        <v>103</v>
       </c>
       <c r="O163" t="n">
-        <v>249</v>
+        <v>103</v>
       </c>
       <c r="R163" t="n">
-        <v>0.2033852934838758</v>
+        <v>0.02950989276752467</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -27999,42 +27999,42 @@
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28066,12 +28066,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -28096,7 +28096,7 @@
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M164" t="inlineStr">
@@ -28105,13 +28105,13 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>68</v>
+        <v>249</v>
       </c>
       <c r="O164" t="n">
-        <v>68</v>
+        <v>249</v>
       </c>
       <c r="R164" t="n">
-        <v>0.01948225930283182</v>
+        <v>0.2033852934838758</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -28144,42 +28144,42 @@
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28211,12 +28211,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -28241,7 +28241,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M165" t="inlineStr">
@@ -28250,13 +28250,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="O165" t="n">
-        <v>185</v>
+        <v>68</v>
       </c>
       <c r="R165" t="n">
-        <v>0.1511095553996668</v>
+        <v>0.01948225930283182</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -28289,42 +28289,42 @@
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28356,12 +28356,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -28386,7 +28386,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -28395,13 +28395,13 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="O166" t="n">
-        <v>72</v>
+        <v>185</v>
       </c>
       <c r="R166" t="n">
-        <v>0.02062827455593957</v>
+        <v>0.1511095553996668</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -28434,40 +28434,185 @@
       </c>
       <c r="AV166" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW166" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX166" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY166" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA166" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB166" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC166" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>tuberculosis</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>D025</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Tuberculosis</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>肺结核</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N167" t="n">
+        <v>72</v>
+      </c>
+      <c r="O167" t="n">
+        <v>72</v>
+      </c>
+      <c r="R167" t="n">
+        <v>0.02062827455593957</v>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
+      <c r="AT167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU167" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV167" t="inlineStr">
+        <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW166" t="inlineStr">
+      <c r="AW167" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX166" t="inlineStr">
+      <c r="AX167" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY166" t="inlineStr">
+      <c r="AY167" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ166" t="inlineStr">
+      <c r="AZ167" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA166" t="inlineStr">
+      <c r="BA167" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB166" t="inlineStr">
+      <c r="BB167" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC166" t="inlineStr">
+      <c r="BC167" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -28589,7 +28734,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10">
@@ -28599,7 +28744,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -28651,7 +28796,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>407741</v>
+        <v>408025</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d025/2026-2029.xlsx
+++ b/diseases/d025/2026-2029.xlsx
@@ -44094,13 +44094,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O244" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="R244" t="n">
-        <v>0.5656130202060476</v>
+        <v>0.5619402083865279</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -48461,13 +48461,13 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O269" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R269" t="n">
-        <v>0.2134571005036965</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
@@ -48625,10 +48625,10 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O270" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U270" t="inlineStr">
         <is>
@@ -51513,13 +51513,13 @@
         </is>
       </c>
       <c r="N287" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O287" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="R287" t="n">
-        <v>0.4517558538009342</v>
+        <v>0.4480830419814144</v>
       </c>
       <c r="S287" t="inlineStr">
         <is>
@@ -54905,13 +54905,13 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O309" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R309" t="n">
-        <v>0.02938249455615832</v>
+        <v>0.04407374183423748</v>
       </c>
       <c r="S309" t="inlineStr">
         <is>
@@ -55050,13 +55050,13 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O310" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R310" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
@@ -55214,10 +55214,10 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O311" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U311" t="inlineStr">
         <is>
@@ -55967,7 +55967,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>560509</v>
+        <v>560514</v>
       </c>
     </row>
     <row r="16">
